--- a/artfynd/A 31480-2025 artfynd.xlsx
+++ b/artfynd/A 31480-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129410998</v>
       </c>
       <c r="B2" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129410984</v>
       </c>
       <c r="B3" t="n">
-        <v>97576</v>
+        <v>97577</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1762,54 +1762,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129406582</v>
+        <v>129411005</v>
       </c>
       <c r="B13" t="n">
-        <v>98705</v>
+        <v>79041</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Björnloken, Björnloken, Ång</t>
+          <t>Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>559263</v>
+        <v>559251</v>
       </c>
       <c r="R13" t="n">
-        <v>7064434</v>
+        <v>7064533</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1839,19 +1830,9 @@
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>15:24</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>15:24</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1866,57 +1847,66 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129411005</v>
+        <v>129406582</v>
       </c>
       <c r="B14" t="n">
-        <v>79041</v>
+        <v>98706</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Spångmyran, Ång</t>
+          <t>Björnloken, Björnloken, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>559251</v>
+        <v>559263</v>
       </c>
       <c r="R14" t="n">
-        <v>7064533</v>
+        <v>7064434</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1946,9 +1936,19 @@
           <t>2025-10-29</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>15:24</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1963,12 +1963,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>

--- a/artfynd/A 31480-2025 artfynd.xlsx
+++ b/artfynd/A 31480-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129410998</v>
       </c>
       <c r="B2" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129410984</v>
       </c>
       <c r="B3" t="n">
-        <v>97577</v>
+        <v>97581</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1076,7 +1076,7 @@
         <v>129410988</v>
       </c>
       <c r="B6" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
         <v>129411001</v>
       </c>
       <c r="B7" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1267,10 +1267,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129410974</v>
+        <v>129411004</v>
       </c>
       <c r="B8" t="n">
-        <v>57727</v>
+        <v>79043</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1278,21 +1278,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1302,10 +1302,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>559243</v>
+        <v>559356</v>
       </c>
       <c r="R8" t="n">
-        <v>7064446</v>
+        <v>7064542</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1338,11 +1338,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1369,32 +1364,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129411004</v>
+        <v>129410962</v>
       </c>
       <c r="B9" t="n">
-        <v>79041</v>
+        <v>80177</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1404,10 +1399,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>559356</v>
+        <v>559237</v>
       </c>
       <c r="R9" t="n">
-        <v>7064542</v>
+        <v>7064501</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1466,32 +1461,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129410962</v>
+        <v>129410974</v>
       </c>
       <c r="B10" t="n">
-        <v>80175</v>
+        <v>57727</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1501,10 +1496,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>559237</v>
+        <v>559243</v>
       </c>
       <c r="R10" t="n">
-        <v>7064501</v>
+        <v>7064446</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1537,6 +1532,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1566,7 +1566,7 @@
         <v>129410987</v>
       </c>
       <c r="B11" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1765,7 +1765,7 @@
         <v>129411005</v>
       </c>
       <c r="B13" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1862,7 +1862,7 @@
         <v>129406582</v>
       </c>
       <c r="B14" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1978,7 +1978,7 @@
         <v>129410961</v>
       </c>
       <c r="B15" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 31480-2025 artfynd.xlsx
+++ b/artfynd/A 31480-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129410998</v>
       </c>
       <c r="B2" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129410984</v>
       </c>
       <c r="B3" t="n">
-        <v>97581</v>
+        <v>97583</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1076,7 +1076,7 @@
         <v>129410988</v>
       </c>
       <c r="B6" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
         <v>129411001</v>
       </c>
       <c r="B7" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1267,32 +1267,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129411004</v>
+        <v>129410962</v>
       </c>
       <c r="B8" t="n">
-        <v>79043</v>
+        <v>80178</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1302,10 +1302,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>559356</v>
+        <v>559237</v>
       </c>
       <c r="R8" t="n">
-        <v>7064542</v>
+        <v>7064501</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1364,32 +1364,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129410962</v>
+        <v>129411004</v>
       </c>
       <c r="B9" t="n">
-        <v>80177</v>
+        <v>79044</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1399,10 +1399,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>559237</v>
+        <v>559356</v>
       </c>
       <c r="R9" t="n">
-        <v>7064501</v>
+        <v>7064542</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1566,7 +1566,7 @@
         <v>129410987</v>
       </c>
       <c r="B11" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1762,45 +1762,54 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129411005</v>
+        <v>129406582</v>
       </c>
       <c r="B13" t="n">
-        <v>79043</v>
+        <v>98712</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Spångmyran, Ång</t>
+          <t>Björnloken, Björnloken, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>559251</v>
+        <v>559263</v>
       </c>
       <c r="R13" t="n">
-        <v>7064533</v>
+        <v>7064434</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1830,9 +1839,19 @@
           <t>2025-10-29</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>15:24</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1847,66 +1866,57 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129406582</v>
+        <v>129411005</v>
       </c>
       <c r="B14" t="n">
-        <v>98710</v>
+        <v>79044</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Björnloken, Björnloken, Ång</t>
+          <t>Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>559263</v>
+        <v>559251</v>
       </c>
       <c r="R14" t="n">
-        <v>7064434</v>
+        <v>7064533</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1936,19 +1946,9 @@
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>15:24</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>15:24</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1963,12 +1963,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -1978,7 +1978,7 @@
         <v>129410961</v>
       </c>
       <c r="B15" t="n">
-        <v>91543</v>
+        <v>91545</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 31480-2025 artfynd.xlsx
+++ b/artfynd/A 31480-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129410998</v>
       </c>
       <c r="B2" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129410984</v>
       </c>
       <c r="B3" t="n">
-        <v>97583</v>
+        <v>97587</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1267,32 +1267,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129410962</v>
+        <v>129411004</v>
       </c>
       <c r="B8" t="n">
-        <v>80178</v>
+        <v>79044</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1302,10 +1302,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>559237</v>
+        <v>559356</v>
       </c>
       <c r="R8" t="n">
-        <v>7064501</v>
+        <v>7064542</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1364,10 +1364,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129411004</v>
+        <v>129410974</v>
       </c>
       <c r="B9" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1375,21 +1375,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1399,10 +1399,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>559356</v>
+        <v>559243</v>
       </c>
       <c r="R9" t="n">
-        <v>7064542</v>
+        <v>7064446</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1435,6 +1435,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1461,32 +1466,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129410974</v>
+        <v>129410962</v>
       </c>
       <c r="B10" t="n">
-        <v>57727</v>
+        <v>80178</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1496,10 +1501,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>559243</v>
+        <v>559237</v>
       </c>
       <c r="R10" t="n">
-        <v>7064446</v>
+        <v>7064501</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1532,11 +1537,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1762,54 +1762,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129406582</v>
+        <v>129411005</v>
       </c>
       <c r="B13" t="n">
-        <v>98712</v>
+        <v>79044</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Björnloken, Björnloken, Ång</t>
+          <t>Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>559263</v>
+        <v>559251</v>
       </c>
       <c r="R13" t="n">
-        <v>7064434</v>
+        <v>7064533</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1839,19 +1830,9 @@
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>15:24</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>15:24</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1866,57 +1847,66 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129411005</v>
+        <v>129406582</v>
       </c>
       <c r="B14" t="n">
-        <v>79044</v>
+        <v>98716</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Spångmyran, Ång</t>
+          <t>Björnloken, Björnloken, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>559251</v>
+        <v>559263</v>
       </c>
       <c r="R14" t="n">
-        <v>7064533</v>
+        <v>7064434</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1946,9 +1936,19 @@
           <t>2025-10-29</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>15:24</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1963,12 +1963,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -1978,7 +1978,7 @@
         <v>129410961</v>
       </c>
       <c r="B15" t="n">
-        <v>91545</v>
+        <v>91549</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 31480-2025 artfynd.xlsx
+++ b/artfynd/A 31480-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129410998</v>
       </c>
       <c r="B2" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129410984</v>
       </c>
       <c r="B3" t="n">
-        <v>97587</v>
+        <v>97595</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1364,32 +1364,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129410974</v>
+        <v>129410962</v>
       </c>
       <c r="B9" t="n">
-        <v>57727</v>
+        <v>80178</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1399,10 +1399,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>559243</v>
+        <v>559237</v>
       </c>
       <c r="R9" t="n">
-        <v>7064446</v>
+        <v>7064501</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1435,11 +1435,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1466,32 +1461,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129410962</v>
+        <v>129410974</v>
       </c>
       <c r="B10" t="n">
-        <v>80178</v>
+        <v>57727</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1501,10 +1496,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>559237</v>
+        <v>559243</v>
       </c>
       <c r="R10" t="n">
-        <v>7064501</v>
+        <v>7064446</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1537,6 +1532,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1762,45 +1762,54 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129411005</v>
+        <v>129406582</v>
       </c>
       <c r="B13" t="n">
-        <v>79044</v>
+        <v>98724</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Spångmyran, Ång</t>
+          <t>Björnloken, Björnloken, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>559251</v>
+        <v>559263</v>
       </c>
       <c r="R13" t="n">
-        <v>7064533</v>
+        <v>7064434</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1830,9 +1839,19 @@
           <t>2025-10-29</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>15:24</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1847,66 +1866,57 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129406582</v>
+        <v>129411005</v>
       </c>
       <c r="B14" t="n">
-        <v>98716</v>
+        <v>79044</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Björnloken, Björnloken, Ång</t>
+          <t>Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>559263</v>
+        <v>559251</v>
       </c>
       <c r="R14" t="n">
-        <v>7064434</v>
+        <v>7064533</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1936,19 +1946,9 @@
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>15:24</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>15:24</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1963,12 +1963,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -1978,7 +1978,7 @@
         <v>129410961</v>
       </c>
       <c r="B15" t="n">
-        <v>91549</v>
+        <v>91550</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 31480-2025 artfynd.xlsx
+++ b/artfynd/A 31480-2025 artfynd.xlsx
@@ -1762,54 +1762,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129406582</v>
+        <v>129411005</v>
       </c>
       <c r="B13" t="n">
-        <v>98724</v>
+        <v>79044</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Björnloken, Björnloken, Ång</t>
+          <t>Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>559263</v>
+        <v>559251</v>
       </c>
       <c r="R13" t="n">
-        <v>7064434</v>
+        <v>7064533</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1839,19 +1830,9 @@
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>15:24</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>15:24</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1866,57 +1847,66 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129411005</v>
+        <v>129406582</v>
       </c>
       <c r="B14" t="n">
-        <v>79044</v>
+        <v>98724</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Spångmyran, Ång</t>
+          <t>Björnloken, Björnloken, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>559251</v>
+        <v>559263</v>
       </c>
       <c r="R14" t="n">
-        <v>7064533</v>
+        <v>7064434</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1946,9 +1936,19 @@
           <t>2025-10-29</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>15:24</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1963,12 +1963,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>

--- a/artfynd/A 31480-2025 artfynd.xlsx
+++ b/artfynd/A 31480-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AY19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1267,10 +1267,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129411004</v>
+        <v>129410974</v>
       </c>
       <c r="B8" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1278,21 +1278,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1302,10 +1302,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>559356</v>
+        <v>559243</v>
       </c>
       <c r="R8" t="n">
-        <v>7064542</v>
+        <v>7064446</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1338,6 +1338,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1364,32 +1369,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129410962</v>
+        <v>129411004</v>
       </c>
       <c r="B9" t="n">
-        <v>80178</v>
+        <v>79044</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1399,10 +1404,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>559237</v>
+        <v>559356</v>
       </c>
       <c r="R9" t="n">
-        <v>7064501</v>
+        <v>7064542</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1461,32 +1466,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129410974</v>
+        <v>129410962</v>
       </c>
       <c r="B10" t="n">
-        <v>57727</v>
+        <v>80178</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1496,10 +1501,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>559243</v>
+        <v>559237</v>
       </c>
       <c r="R10" t="n">
-        <v>7064446</v>
+        <v>7064501</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1532,11 +1537,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1563,10 +1563,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129410987</v>
+        <v>129410972</v>
       </c>
       <c r="B11" t="n">
-        <v>80149</v>
+        <v>57727</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1574,21 +1574,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1598,10 +1598,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>559289</v>
+        <v>559235</v>
       </c>
       <c r="R11" t="n">
-        <v>7064524</v>
+        <v>7064479</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1634,6 +1634,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1660,10 +1665,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129410972</v>
+        <v>129410987</v>
       </c>
       <c r="B12" t="n">
-        <v>57727</v>
+        <v>80149</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1671,21 +1676,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1695,10 +1700,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>559235</v>
+        <v>559289</v>
       </c>
       <c r="R12" t="n">
-        <v>7064479</v>
+        <v>7064524</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1731,11 +1736,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1762,45 +1762,54 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129411005</v>
+        <v>129406582</v>
       </c>
       <c r="B13" t="n">
-        <v>79044</v>
+        <v>98724</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Spångmyran, Ång</t>
+          <t>Björnloken, Björnloken, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>559251</v>
+        <v>559263</v>
       </c>
       <c r="R13" t="n">
-        <v>7064533</v>
+        <v>7064434</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1830,9 +1839,19 @@
           <t>2025-10-29</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>15:24</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1847,66 +1866,57 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129406582</v>
+        <v>129411005</v>
       </c>
       <c r="B14" t="n">
-        <v>98724</v>
+        <v>79044</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Björnloken, Björnloken, Ång</t>
+          <t>Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>559263</v>
+        <v>559251</v>
       </c>
       <c r="R14" t="n">
-        <v>7064434</v>
+        <v>7064533</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1936,19 +1946,9 @@
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>15:24</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>15:24</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1963,12 +1963,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2176,6 +2176,332 @@
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>129555025</v>
+      </c>
+      <c r="B17" t="n">
+        <v>80149</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Mattismyrberget, Mattismyrberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>559581</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7064522</v>
+      </c>
+      <c r="S17" t="n">
+        <v>4</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Fjällsjö</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>12:52</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>12:52</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Peter von Troil</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Peter von Troil</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>129555259</v>
+      </c>
+      <c r="B18" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Mattismyrberget, Mattismyrberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>559440</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7064499</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Fjällsjö</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>13:12</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>13:12</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Peter von Troil</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Peter von Troil</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>129555076</v>
+      </c>
+      <c r="B19" t="n">
+        <v>79044</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Mattismyrberget, Mattismyrberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>559552</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7064528</v>
+      </c>
+      <c r="S19" t="n">
+        <v>4</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Fjällsjö</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>12:57</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>12:57</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Peter von Troil</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Peter von Troil</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 31480-2025 artfynd.xlsx
+++ b/artfynd/A 31480-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129410998</v>
       </c>
       <c r="B2" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129410984</v>
       </c>
       <c r="B3" t="n">
-        <v>97595</v>
+        <v>97598</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1267,10 +1267,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129410974</v>
+        <v>129411004</v>
       </c>
       <c r="B8" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1278,21 +1278,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1302,10 +1302,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>559243</v>
+        <v>559356</v>
       </c>
       <c r="R8" t="n">
-        <v>7064446</v>
+        <v>7064542</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1338,11 +1338,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1369,32 +1364,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129411004</v>
+        <v>129410962</v>
       </c>
       <c r="B9" t="n">
-        <v>79044</v>
+        <v>80178</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1404,10 +1399,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>559356</v>
+        <v>559237</v>
       </c>
       <c r="R9" t="n">
-        <v>7064542</v>
+        <v>7064501</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1466,32 +1461,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129410962</v>
+        <v>129410974</v>
       </c>
       <c r="B10" t="n">
-        <v>80178</v>
+        <v>57727</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1501,10 +1496,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>559237</v>
+        <v>559243</v>
       </c>
       <c r="R10" t="n">
-        <v>7064501</v>
+        <v>7064446</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1537,6 +1532,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1762,54 +1762,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129406582</v>
+        <v>129411005</v>
       </c>
       <c r="B13" t="n">
-        <v>98724</v>
+        <v>79044</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Björnloken, Björnloken, Ång</t>
+          <t>Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>559263</v>
+        <v>559251</v>
       </c>
       <c r="R13" t="n">
-        <v>7064434</v>
+        <v>7064533</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1839,19 +1830,9 @@
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>15:24</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>15:24</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1866,57 +1847,66 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129411005</v>
+        <v>129406582</v>
       </c>
       <c r="B14" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Spångmyran, Ång</t>
+          <t>Björnloken, Björnloken, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>559251</v>
+        <v>559263</v>
       </c>
       <c r="R14" t="n">
-        <v>7064533</v>
+        <v>7064434</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1946,9 +1936,19 @@
           <t>2025-10-29</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>15:24</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1963,12 +1963,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -1978,7 +1978,7 @@
         <v>129410961</v>
       </c>
       <c r="B15" t="n">
-        <v>91550</v>
+        <v>91553</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 31480-2025 artfynd.xlsx
+++ b/artfynd/A 31480-2025 artfynd.xlsx
@@ -1267,10 +1267,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129411004</v>
+        <v>129410974</v>
       </c>
       <c r="B8" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1278,21 +1278,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1302,10 +1302,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>559356</v>
+        <v>559243</v>
       </c>
       <c r="R8" t="n">
-        <v>7064542</v>
+        <v>7064446</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1338,6 +1338,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1364,32 +1369,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129410962</v>
+        <v>129411004</v>
       </c>
       <c r="B9" t="n">
-        <v>80178</v>
+        <v>79044</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1399,10 +1404,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>559237</v>
+        <v>559356</v>
       </c>
       <c r="R9" t="n">
-        <v>7064501</v>
+        <v>7064542</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1461,32 +1466,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129410974</v>
+        <v>129410962</v>
       </c>
       <c r="B10" t="n">
-        <v>57727</v>
+        <v>80178</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1496,10 +1501,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>559243</v>
+        <v>559237</v>
       </c>
       <c r="R10" t="n">
-        <v>7064446</v>
+        <v>7064501</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1532,11 +1537,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1563,10 +1563,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129410972</v>
+        <v>129410987</v>
       </c>
       <c r="B11" t="n">
-        <v>57727</v>
+        <v>80149</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1574,21 +1574,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1598,10 +1598,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>559235</v>
+        <v>559289</v>
       </c>
       <c r="R11" t="n">
-        <v>7064479</v>
+        <v>7064524</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1634,11 +1634,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1665,10 +1660,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129410987</v>
+        <v>129410972</v>
       </c>
       <c r="B12" t="n">
-        <v>80149</v>
+        <v>57727</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1676,21 +1671,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1700,10 +1695,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>559289</v>
+        <v>559235</v>
       </c>
       <c r="R12" t="n">
-        <v>7064524</v>
+        <v>7064479</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1736,6 +1731,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2285,10 +2285,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129555259</v>
+        <v>129555076</v>
       </c>
       <c r="B18" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2296,42 +2296,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Mattismyrberget, Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>559440</v>
+        <v>559552</v>
       </c>
       <c r="R18" t="n">
-        <v>7064499</v>
+        <v>7064528</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2360,7 +2355,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2370,7 +2365,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2397,10 +2392,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129555076</v>
+        <v>129555259</v>
       </c>
       <c r="B19" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2408,37 +2403,45 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Mattismyrberget, Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>559552</v>
+        <v>559440</v>
       </c>
       <c r="R19" t="n">
-        <v>7064528</v>
+        <v>7064499</v>
       </c>
       <c r="S19" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2467,7 +2470,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2477,7 +2480,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>13:12</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD19" t="b">

--- a/artfynd/A 31480-2025 artfynd.xlsx
+++ b/artfynd/A 31480-2025 artfynd.xlsx
@@ -1267,32 +1267,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129410974</v>
+        <v>129410962</v>
       </c>
       <c r="B8" t="n">
-        <v>57727</v>
+        <v>80178</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1302,10 +1302,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>559243</v>
+        <v>559237</v>
       </c>
       <c r="R8" t="n">
-        <v>7064446</v>
+        <v>7064501</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1338,11 +1338,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1466,32 +1461,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129410962</v>
+        <v>129410974</v>
       </c>
       <c r="B10" t="n">
-        <v>80178</v>
+        <v>57727</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1501,10 +1496,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>559237</v>
+        <v>559243</v>
       </c>
       <c r="R10" t="n">
-        <v>7064501</v>
+        <v>7064446</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1537,6 +1532,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1563,10 +1563,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129410987</v>
+        <v>129410972</v>
       </c>
       <c r="B11" t="n">
-        <v>80149</v>
+        <v>57727</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1574,21 +1574,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1598,10 +1598,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>559289</v>
+        <v>559235</v>
       </c>
       <c r="R11" t="n">
-        <v>7064524</v>
+        <v>7064479</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1634,6 +1634,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1660,10 +1665,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129410972</v>
+        <v>129410987</v>
       </c>
       <c r="B12" t="n">
-        <v>57727</v>
+        <v>80149</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1671,21 +1676,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1695,10 +1700,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>559235</v>
+        <v>559289</v>
       </c>
       <c r="R12" t="n">
-        <v>7064479</v>
+        <v>7064524</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1731,11 +1736,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 31480-2025 artfynd.xlsx
+++ b/artfynd/A 31480-2025 artfynd.xlsx
@@ -1267,32 +1267,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129410962</v>
+        <v>129411004</v>
       </c>
       <c r="B8" t="n">
-        <v>80178</v>
+        <v>79044</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1302,10 +1302,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>559237</v>
+        <v>559356</v>
       </c>
       <c r="R8" t="n">
-        <v>7064501</v>
+        <v>7064542</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1364,10 +1364,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129411004</v>
+        <v>129410974</v>
       </c>
       <c r="B9" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1375,21 +1375,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1399,10 +1399,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>559356</v>
+        <v>559243</v>
       </c>
       <c r="R9" t="n">
-        <v>7064542</v>
+        <v>7064446</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1435,6 +1435,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1461,32 +1466,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129410974</v>
+        <v>129410962</v>
       </c>
       <c r="B10" t="n">
-        <v>57727</v>
+        <v>80178</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1496,10 +1501,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>559243</v>
+        <v>559237</v>
       </c>
       <c r="R10" t="n">
-        <v>7064446</v>
+        <v>7064501</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1532,11 +1537,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1563,10 +1563,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129410972</v>
+        <v>129410987</v>
       </c>
       <c r="B11" t="n">
-        <v>57727</v>
+        <v>80149</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1574,21 +1574,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1598,10 +1598,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>559235</v>
+        <v>559289</v>
       </c>
       <c r="R11" t="n">
-        <v>7064479</v>
+        <v>7064524</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1634,11 +1634,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1665,10 +1660,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129410987</v>
+        <v>129410972</v>
       </c>
       <c r="B12" t="n">
-        <v>80149</v>
+        <v>57727</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1676,21 +1671,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1700,10 +1695,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>559289</v>
+        <v>559235</v>
       </c>
       <c r="R12" t="n">
-        <v>7064524</v>
+        <v>7064479</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1736,6 +1731,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 31480-2025 artfynd.xlsx
+++ b/artfynd/A 31480-2025 artfynd.xlsx
@@ -1267,32 +1267,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129411004</v>
+        <v>129410962</v>
       </c>
       <c r="B8" t="n">
-        <v>79044</v>
+        <v>80178</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1302,10 +1302,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>559356</v>
+        <v>559237</v>
       </c>
       <c r="R8" t="n">
-        <v>7064542</v>
+        <v>7064501</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1364,10 +1364,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129410974</v>
+        <v>129411004</v>
       </c>
       <c r="B9" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1375,21 +1375,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1399,10 +1399,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>559243</v>
+        <v>559356</v>
       </c>
       <c r="R9" t="n">
-        <v>7064446</v>
+        <v>7064542</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1435,11 +1435,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1466,32 +1461,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129410962</v>
+        <v>129410974</v>
       </c>
       <c r="B10" t="n">
-        <v>80178</v>
+        <v>57727</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1501,10 +1496,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>559237</v>
+        <v>559243</v>
       </c>
       <c r="R10" t="n">
-        <v>7064501</v>
+        <v>7064446</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1537,6 +1532,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 31480-2025 artfynd.xlsx
+++ b/artfynd/A 31480-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129410998</v>
       </c>
       <c r="B2" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129410984</v>
       </c>
       <c r="B3" t="n">
-        <v>97598</v>
+        <v>97627</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129410973</v>
       </c>
       <c r="B4" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>129410967</v>
       </c>
       <c r="B5" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1076,7 +1076,7 @@
         <v>129410988</v>
       </c>
       <c r="B6" t="n">
-        <v>80149</v>
+        <v>80175</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
         <v>129411001</v>
       </c>
       <c r="B7" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
         <v>129410962</v>
       </c>
       <c r="B8" t="n">
-        <v>80178</v>
+        <v>80204</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>129411004</v>
       </c>
       <c r="B9" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1464,7 +1464,7 @@
         <v>129410974</v>
       </c>
       <c r="B10" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         <v>129410987</v>
       </c>
       <c r="B11" t="n">
-        <v>80149</v>
+        <v>80175</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1663,7 +1663,7 @@
         <v>129410972</v>
       </c>
       <c r="B12" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1762,45 +1762,54 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129411005</v>
+        <v>129406582</v>
       </c>
       <c r="B13" t="n">
-        <v>79044</v>
+        <v>98756</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Spångmyran, Ång</t>
+          <t>Björnloken, Björnloken, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>559251</v>
+        <v>559263</v>
       </c>
       <c r="R13" t="n">
-        <v>7064533</v>
+        <v>7064434</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1830,9 +1839,19 @@
           <t>2025-10-29</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>15:24</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1847,66 +1866,57 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129406582</v>
+        <v>129411005</v>
       </c>
       <c r="B14" t="n">
-        <v>98727</v>
+        <v>79070</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Björnloken, Björnloken, Ång</t>
+          <t>Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>559263</v>
+        <v>559251</v>
       </c>
       <c r="R14" t="n">
-        <v>7064434</v>
+        <v>7064533</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1936,19 +1946,9 @@
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>15:24</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>15:24</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1963,12 +1963,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -1978,7 +1978,7 @@
         <v>129410961</v>
       </c>
       <c r="B15" t="n">
-        <v>91553</v>
+        <v>91581</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2075,7 +2075,7 @@
         <v>129410966</v>
       </c>
       <c r="B16" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2181,7 +2181,7 @@
         <v>129555025</v>
       </c>
       <c r="B17" t="n">
-        <v>80149</v>
+        <v>80175</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2288,7 +2288,7 @@
         <v>129555076</v>
       </c>
       <c r="B18" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2395,7 +2395,7 @@
         <v>129555259</v>
       </c>
       <c r="B19" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 31480-2025 artfynd.xlsx
+++ b/artfynd/A 31480-2025 artfynd.xlsx
@@ -1762,54 +1762,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129406582</v>
+        <v>129411005</v>
       </c>
       <c r="B13" t="n">
-        <v>98756</v>
+        <v>79070</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Björnloken, Björnloken, Ång</t>
+          <t>Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>559263</v>
+        <v>559251</v>
       </c>
       <c r="R13" t="n">
-        <v>7064434</v>
+        <v>7064533</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1839,19 +1830,9 @@
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>15:24</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>15:24</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1866,57 +1847,66 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129411005</v>
+        <v>129406582</v>
       </c>
       <c r="B14" t="n">
-        <v>79070</v>
+        <v>98756</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Spångmyran, Ång</t>
+          <t>Björnloken, Björnloken, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>559251</v>
+        <v>559263</v>
       </c>
       <c r="R14" t="n">
-        <v>7064533</v>
+        <v>7064434</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1946,9 +1936,19 @@
           <t>2025-10-29</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>15:24</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1963,12 +1963,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>

--- a/artfynd/A 31480-2025 artfynd.xlsx
+++ b/artfynd/A 31480-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129410998</v>
       </c>
       <c r="B2" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129410984</v>
       </c>
       <c r="B3" t="n">
-        <v>97627</v>
+        <v>97639</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129410973</v>
       </c>
       <c r="B4" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>129410967</v>
       </c>
       <c r="B5" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1076,7 +1076,7 @@
         <v>129410988</v>
       </c>
       <c r="B6" t="n">
-        <v>80175</v>
+        <v>80180</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
         <v>129411001</v>
       </c>
       <c r="B7" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1267,32 +1267,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129410962</v>
+        <v>129411004</v>
       </c>
       <c r="B8" t="n">
-        <v>80204</v>
+        <v>79075</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1302,10 +1302,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>559237</v>
+        <v>559356</v>
       </c>
       <c r="R8" t="n">
-        <v>7064501</v>
+        <v>7064542</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1364,32 +1364,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129411004</v>
+        <v>129410962</v>
       </c>
       <c r="B9" t="n">
-        <v>79070</v>
+        <v>80209</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1399,10 +1399,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>559356</v>
+        <v>559237</v>
       </c>
       <c r="R9" t="n">
-        <v>7064542</v>
+        <v>7064501</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1464,7 +1464,7 @@
         <v>129410974</v>
       </c>
       <c r="B10" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1563,10 +1563,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129410987</v>
+        <v>129410972</v>
       </c>
       <c r="B11" t="n">
-        <v>80175</v>
+        <v>57735</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1574,21 +1574,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1598,10 +1598,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>559289</v>
+        <v>559235</v>
       </c>
       <c r="R11" t="n">
-        <v>7064524</v>
+        <v>7064479</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1634,6 +1634,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1660,10 +1665,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129410972</v>
+        <v>129410987</v>
       </c>
       <c r="B12" t="n">
-        <v>57730</v>
+        <v>80180</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1671,21 +1676,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1695,10 +1700,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>559235</v>
+        <v>559289</v>
       </c>
       <c r="R12" t="n">
-        <v>7064479</v>
+        <v>7064524</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1731,11 +1736,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1765,7 +1765,7 @@
         <v>129411005</v>
       </c>
       <c r="B13" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1862,7 +1862,7 @@
         <v>129406582</v>
       </c>
       <c r="B14" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1978,7 +1978,7 @@
         <v>129410961</v>
       </c>
       <c r="B15" t="n">
-        <v>91581</v>
+        <v>91587</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2075,7 +2075,7 @@
         <v>129410966</v>
       </c>
       <c r="B16" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2181,7 +2181,7 @@
         <v>129555025</v>
       </c>
       <c r="B17" t="n">
-        <v>80175</v>
+        <v>80180</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2288,7 +2288,7 @@
         <v>129555076</v>
       </c>
       <c r="B18" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2395,7 +2395,7 @@
         <v>129555259</v>
       </c>
       <c r="B19" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 31480-2025 artfynd.xlsx
+++ b/artfynd/A 31480-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129410998</v>
       </c>
       <c r="B2" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129410984</v>
       </c>
       <c r="B3" t="n">
-        <v>97639</v>
+        <v>97640</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129410973</v>
       </c>
       <c r="B4" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>129410967</v>
       </c>
       <c r="B5" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1076,7 +1076,7 @@
         <v>129410988</v>
       </c>
       <c r="B6" t="n">
-        <v>80180</v>
+        <v>80181</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
         <v>129411001</v>
       </c>
       <c r="B7" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
         <v>129411004</v>
       </c>
       <c r="B8" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1364,32 +1364,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129410962</v>
+        <v>129410974</v>
       </c>
       <c r="B9" t="n">
-        <v>80209</v>
+        <v>57736</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1399,10 +1399,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>559237</v>
+        <v>559243</v>
       </c>
       <c r="R9" t="n">
-        <v>7064501</v>
+        <v>7064446</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1435,6 +1435,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1461,32 +1466,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129410974</v>
+        <v>129410962</v>
       </c>
       <c r="B10" t="n">
-        <v>57735</v>
+        <v>80210</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1496,10 +1501,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>559243</v>
+        <v>559237</v>
       </c>
       <c r="R10" t="n">
-        <v>7064446</v>
+        <v>7064501</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1532,11 +1537,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1566,7 +1566,7 @@
         <v>129410972</v>
       </c>
       <c r="B11" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1668,7 +1668,7 @@
         <v>129410987</v>
       </c>
       <c r="B12" t="n">
-        <v>80180</v>
+        <v>80181</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1765,7 +1765,7 @@
         <v>129411005</v>
       </c>
       <c r="B13" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1862,7 +1862,7 @@
         <v>129406582</v>
       </c>
       <c r="B14" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1978,7 +1978,7 @@
         <v>129410961</v>
       </c>
       <c r="B15" t="n">
-        <v>91587</v>
+        <v>91588</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2075,7 +2075,7 @@
         <v>129410966</v>
       </c>
       <c r="B16" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2181,7 +2181,7 @@
         <v>129555025</v>
       </c>
       <c r="B17" t="n">
-        <v>80180</v>
+        <v>80181</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2288,7 +2288,7 @@
         <v>129555076</v>
       </c>
       <c r="B18" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2395,7 +2395,7 @@
         <v>129555259</v>
       </c>
       <c r="B19" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 31480-2025 artfynd.xlsx
+++ b/artfynd/A 31480-2025 artfynd.xlsx
@@ -1762,45 +1762,54 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129411005</v>
+        <v>129406582</v>
       </c>
       <c r="B13" t="n">
-        <v>79076</v>
+        <v>98769</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Spångmyran, Ång</t>
+          <t>Björnloken, Björnloken, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>559251</v>
+        <v>559263</v>
       </c>
       <c r="R13" t="n">
-        <v>7064533</v>
+        <v>7064434</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1830,9 +1839,19 @@
           <t>2025-10-29</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>15:24</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1847,66 +1866,57 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129406582</v>
+        <v>129411005</v>
       </c>
       <c r="B14" t="n">
-        <v>98769</v>
+        <v>79076</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Björnloken, Björnloken, Ång</t>
+          <t>Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>559263</v>
+        <v>559251</v>
       </c>
       <c r="R14" t="n">
-        <v>7064434</v>
+        <v>7064533</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1936,19 +1946,9 @@
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>15:24</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>15:24</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1963,12 +1963,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>

--- a/artfynd/A 31480-2025 artfynd.xlsx
+++ b/artfynd/A 31480-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129410998</v>
       </c>
       <c r="B2" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129410984</v>
       </c>
       <c r="B3" t="n">
-        <v>97640</v>
+        <v>97645</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1076,7 +1076,7 @@
         <v>129410988</v>
       </c>
       <c r="B6" t="n">
-        <v>80181</v>
+        <v>80186</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
         <v>129411001</v>
       </c>
       <c r="B7" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
         <v>129411004</v>
       </c>
       <c r="B8" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1364,32 +1364,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129410974</v>
+        <v>129410962</v>
       </c>
       <c r="B9" t="n">
-        <v>57736</v>
+        <v>80215</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1399,10 +1399,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>559243</v>
+        <v>559237</v>
       </c>
       <c r="R9" t="n">
-        <v>7064446</v>
+        <v>7064501</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1435,11 +1435,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1466,32 +1461,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129410962</v>
+        <v>129410974</v>
       </c>
       <c r="B10" t="n">
-        <v>80210</v>
+        <v>57736</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1501,10 +1496,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>559237</v>
+        <v>559243</v>
       </c>
       <c r="R10" t="n">
-        <v>7064501</v>
+        <v>7064446</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1537,6 +1532,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1563,10 +1563,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129410972</v>
+        <v>129410987</v>
       </c>
       <c r="B11" t="n">
-        <v>57736</v>
+        <v>80186</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1574,21 +1574,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1598,10 +1598,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>559235</v>
+        <v>559289</v>
       </c>
       <c r="R11" t="n">
-        <v>7064479</v>
+        <v>7064524</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1634,11 +1634,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1665,10 +1660,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129410987</v>
+        <v>129410972</v>
       </c>
       <c r="B12" t="n">
-        <v>80181</v>
+        <v>57736</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1676,21 +1671,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1700,10 +1695,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>559289</v>
+        <v>559235</v>
       </c>
       <c r="R12" t="n">
-        <v>7064524</v>
+        <v>7064479</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1736,6 +1731,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1762,54 +1762,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129406582</v>
+        <v>129411005</v>
       </c>
       <c r="B13" t="n">
-        <v>98769</v>
+        <v>79081</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Björnloken, Björnloken, Ång</t>
+          <t>Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>559263</v>
+        <v>559251</v>
       </c>
       <c r="R13" t="n">
-        <v>7064434</v>
+        <v>7064533</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1839,19 +1830,9 @@
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>15:24</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>15:24</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1866,57 +1847,66 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129411005</v>
+        <v>129406582</v>
       </c>
       <c r="B14" t="n">
-        <v>79076</v>
+        <v>98774</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Spångmyran, Ång</t>
+          <t>Björnloken, Björnloken, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>559251</v>
+        <v>559263</v>
       </c>
       <c r="R14" t="n">
-        <v>7064533</v>
+        <v>7064434</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1946,9 +1936,19 @@
           <t>2025-10-29</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>15:24</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1963,12 +1963,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -1978,7 +1978,7 @@
         <v>129410961</v>
       </c>
       <c r="B15" t="n">
-        <v>91588</v>
+        <v>91593</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2181,7 +2181,7 @@
         <v>129555025</v>
       </c>
       <c r="B17" t="n">
-        <v>80181</v>
+        <v>80186</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2288,7 +2288,7 @@
         <v>129555076</v>
       </c>
       <c r="B18" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 31480-2025 artfynd.xlsx
+++ b/artfynd/A 31480-2025 artfynd.xlsx
@@ -1267,32 +1267,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129411004</v>
+        <v>129410962</v>
       </c>
       <c r="B8" t="n">
-        <v>79081</v>
+        <v>80215</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1302,10 +1302,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>559356</v>
+        <v>559237</v>
       </c>
       <c r="R8" t="n">
-        <v>7064542</v>
+        <v>7064501</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1364,32 +1364,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129410962</v>
+        <v>129410974</v>
       </c>
       <c r="B9" t="n">
-        <v>80215</v>
+        <v>57736</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1399,10 +1399,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>559237</v>
+        <v>559243</v>
       </c>
       <c r="R9" t="n">
-        <v>7064501</v>
+        <v>7064446</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1435,6 +1435,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1461,10 +1466,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129410974</v>
+        <v>129411004</v>
       </c>
       <c r="B10" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1472,21 +1477,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1496,10 +1501,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>559243</v>
+        <v>559356</v>
       </c>
       <c r="R10" t="n">
-        <v>7064446</v>
+        <v>7064542</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1532,11 +1537,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1762,45 +1762,54 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129411005</v>
+        <v>129406582</v>
       </c>
       <c r="B13" t="n">
-        <v>79081</v>
+        <v>98774</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Spångmyran, Ång</t>
+          <t>Björnloken, Björnloken, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>559251</v>
+        <v>559263</v>
       </c>
       <c r="R13" t="n">
-        <v>7064533</v>
+        <v>7064434</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1830,9 +1839,19 @@
           <t>2025-10-29</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>15:24</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1847,66 +1866,57 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129406582</v>
+        <v>129411005</v>
       </c>
       <c r="B14" t="n">
-        <v>98774</v>
+        <v>79081</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Björnloken, Björnloken, Ång</t>
+          <t>Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>559263</v>
+        <v>559251</v>
       </c>
       <c r="R14" t="n">
-        <v>7064434</v>
+        <v>7064533</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1936,19 +1946,9 @@
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>15:24</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>15:24</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1963,12 +1963,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>

--- a/artfynd/A 31480-2025 artfynd.xlsx
+++ b/artfynd/A 31480-2025 artfynd.xlsx
@@ -1762,54 +1762,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129406582</v>
+        <v>129411005</v>
       </c>
       <c r="B13" t="n">
-        <v>98774</v>
+        <v>79081</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Björnloken, Björnloken, Ång</t>
+          <t>Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>559263</v>
+        <v>559251</v>
       </c>
       <c r="R13" t="n">
-        <v>7064434</v>
+        <v>7064533</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1839,19 +1830,9 @@
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>15:24</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>15:24</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1866,57 +1847,66 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129411005</v>
+        <v>129406582</v>
       </c>
       <c r="B14" t="n">
-        <v>79081</v>
+        <v>98774</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Spångmyran, Ång</t>
+          <t>Björnloken, Björnloken, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>559251</v>
+        <v>559263</v>
       </c>
       <c r="R14" t="n">
-        <v>7064533</v>
+        <v>7064434</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1946,9 +1936,19 @@
           <t>2025-10-29</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>15:24</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1963,12 +1963,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>

--- a/artfynd/A 31480-2025 artfynd.xlsx
+++ b/artfynd/A 31480-2025 artfynd.xlsx
@@ -1267,32 +1267,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129410962</v>
+        <v>129411004</v>
       </c>
       <c r="B8" t="n">
-        <v>80215</v>
+        <v>79081</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1302,10 +1302,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>559237</v>
+        <v>559356</v>
       </c>
       <c r="R8" t="n">
-        <v>7064501</v>
+        <v>7064542</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1364,32 +1364,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129410974</v>
+        <v>129410962</v>
       </c>
       <c r="B9" t="n">
-        <v>57736</v>
+        <v>80215</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1399,10 +1399,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>559243</v>
+        <v>559237</v>
       </c>
       <c r="R9" t="n">
-        <v>7064446</v>
+        <v>7064501</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1435,11 +1435,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1466,10 +1461,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129411004</v>
+        <v>129410974</v>
       </c>
       <c r="B10" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1477,21 +1472,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1501,10 +1496,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>559356</v>
+        <v>559243</v>
       </c>
       <c r="R10" t="n">
-        <v>7064542</v>
+        <v>7064446</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1537,6 +1532,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 31480-2025 artfynd.xlsx
+++ b/artfynd/A 31480-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129410998</v>
       </c>
       <c r="B2" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129410984</v>
       </c>
       <c r="B3" t="n">
-        <v>97645</v>
+        <v>97649</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1267,32 +1267,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129411004</v>
+        <v>129410962</v>
       </c>
       <c r="B8" t="n">
-        <v>79081</v>
+        <v>80215</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1302,10 +1302,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>559356</v>
+        <v>559237</v>
       </c>
       <c r="R8" t="n">
-        <v>7064542</v>
+        <v>7064501</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1364,32 +1364,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129410962</v>
+        <v>129410974</v>
       </c>
       <c r="B9" t="n">
-        <v>80215</v>
+        <v>57736</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1399,10 +1399,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>559237</v>
+        <v>559243</v>
       </c>
       <c r="R9" t="n">
-        <v>7064501</v>
+        <v>7064446</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1435,6 +1435,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1461,10 +1466,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129410974</v>
+        <v>129411004</v>
       </c>
       <c r="B10" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1472,21 +1477,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1496,10 +1501,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>559243</v>
+        <v>559356</v>
       </c>
       <c r="R10" t="n">
-        <v>7064446</v>
+        <v>7064542</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1532,11 +1537,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1563,10 +1563,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129410987</v>
+        <v>129410972</v>
       </c>
       <c r="B11" t="n">
-        <v>80186</v>
+        <v>57736</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1574,21 +1574,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1598,10 +1598,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>559289</v>
+        <v>559235</v>
       </c>
       <c r="R11" t="n">
-        <v>7064524</v>
+        <v>7064479</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1634,6 +1634,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1660,10 +1665,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129410972</v>
+        <v>129410987</v>
       </c>
       <c r="B12" t="n">
-        <v>57736</v>
+        <v>80186</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1671,21 +1676,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1695,10 +1700,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>559235</v>
+        <v>559289</v>
       </c>
       <c r="R12" t="n">
-        <v>7064479</v>
+        <v>7064524</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1731,11 +1736,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1862,7 +1862,7 @@
         <v>129406582</v>
       </c>
       <c r="B14" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1978,7 +1978,7 @@
         <v>129410961</v>
       </c>
       <c r="B15" t="n">
-        <v>91593</v>
+        <v>91597</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 31480-2025 artfynd.xlsx
+++ b/artfynd/A 31480-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129410998</v>
       </c>
       <c r="B2" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129410984</v>
       </c>
       <c r="B3" t="n">
-        <v>97649</v>
+        <v>97651</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1267,32 +1267,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129410962</v>
+        <v>129411004</v>
       </c>
       <c r="B8" t="n">
-        <v>80215</v>
+        <v>79081</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1302,10 +1302,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>559237</v>
+        <v>559356</v>
       </c>
       <c r="R8" t="n">
-        <v>7064501</v>
+        <v>7064542</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1364,32 +1364,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129410974</v>
+        <v>129410962</v>
       </c>
       <c r="B9" t="n">
-        <v>57736</v>
+        <v>80215</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1399,10 +1399,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>559243</v>
+        <v>559237</v>
       </c>
       <c r="R9" t="n">
-        <v>7064446</v>
+        <v>7064501</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1435,11 +1435,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1466,10 +1461,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129411004</v>
+        <v>129410974</v>
       </c>
       <c r="B10" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1477,21 +1472,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1501,10 +1496,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>559356</v>
+        <v>559243</v>
       </c>
       <c r="R10" t="n">
-        <v>7064542</v>
+        <v>7064446</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1537,6 +1532,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1563,10 +1563,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129410972</v>
+        <v>129410987</v>
       </c>
       <c r="B11" t="n">
-        <v>57736</v>
+        <v>80186</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1574,21 +1574,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1598,10 +1598,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>559235</v>
+        <v>559289</v>
       </c>
       <c r="R11" t="n">
-        <v>7064479</v>
+        <v>7064524</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1634,11 +1634,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1665,10 +1660,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129410987</v>
+        <v>129410972</v>
       </c>
       <c r="B12" t="n">
-        <v>80186</v>
+        <v>57736</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1676,21 +1671,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1700,10 +1695,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>559289</v>
+        <v>559235</v>
       </c>
       <c r="R12" t="n">
-        <v>7064524</v>
+        <v>7064479</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1736,6 +1731,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1862,7 +1862,7 @@
         <v>129406582</v>
       </c>
       <c r="B14" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1978,7 +1978,7 @@
         <v>129410961</v>
       </c>
       <c r="B15" t="n">
-        <v>91597</v>
+        <v>91599</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 31480-2025 artfynd.xlsx
+++ b/artfynd/A 31480-2025 artfynd.xlsx
@@ -2181,7 +2181,7 @@
         <v>129555025</v>
       </c>
       <c r="B17" t="n">
-        <v>80186</v>
+        <v>80189</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2288,7 +2288,7 @@
         <v>129555076</v>
       </c>
       <c r="B18" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2395,7 +2395,7 @@
         <v>129555259</v>
       </c>
       <c r="B19" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 31480-2025 artfynd.xlsx
+++ b/artfynd/A 31480-2025 artfynd.xlsx
@@ -2395,7 +2395,7 @@
         <v>129555259</v>
       </c>
       <c r="B19" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
